--- a/Ministry_of_Education_and_Higher_Education.xlsx
+++ b/Ministry_of_Education_and_Higher_Education.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E194"/>
+  <dimension ref="A1:E205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8331,6 +8331,497 @@
         </is>
       </c>
     </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>وزارة التربية وبنك التنمية الألماني يُطلقان برنامجاً لتحديث وبناء المدارس الرسمية في لبنان</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D9%88%D8%B2%D8%A7%D8%B1%D8%A9-%D8%A7%D9%84%D8%AA%D8%B1%D8%A8%D9%8A%D8%A9-%D9%88%D8%A8%D9%86%D9%83-%D8%A7%D9%84%D8%AA%D9%86%D9%85%D9%8A%D8%A9-%D8%A7%D9%84%D8%A3%D9%84%D9%85%D8%A7%D9%86%D9%8A-%D9%8A%D9%8F%D8%B7%D9%84%D9%82%D8%A7%D9%86-%D8%A8%D8%B1%D9%86%D8%A7%D9%85%D8%AC%D8%A7%D9%8B-%D9%84%D8%AA%D8%AD%D8%AF%D9%8A%D8%AB-%D9%88%D8%A8%D9%86%D8%A7%D8%A1-%D8%A7%D9%84%D9%85%D8%AF%D8%A7%D8%B1%D8%B3-%D8%A7%D9%84%D8%B1%D8%B3%D9%85%D9%8A%D8%A9</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>وزارة التربية وبنك التنمية الألماني يُطلقان برنامجاً لتحديث وبناء المدارس الرسمية في لبنان
+أعلنت وزارة التربية والتعليم العالي، بالتعاون مع بنك التنمية الألماني (KfW) والحكومة الألمانية، عن المضي قُدماً في تنفيذ "برنامج بناء وتوسعة المدارس الرسمية".
+يهدف البرنامج إلى توفير أكثر من 4,000 مقعد دراسي جديد وتحديث البنية التحتية التعليمية لضمان بيئة آمنة وشاملة للطلاب، وذلك من خلال مرحلتين:
+* المرحلة الأولى: إنشاء ما لا يقل عن 4 مدارس رسمية جديدة بدعم وتمويل ألماني.
+* المرحلة الثانية: توسعة وترميم مجموعة من المدارس القائمة وتزويدها بالتجهيزات الحديثة، إضافة إلى استخدام تقنيات الطاقة الشمسية وتجميع مياه الأمطار.
+وأكّدت الوزارة التزام المشروع الكامل بأعلى المعايير البيئية والاجتماعية والسلامة العامة، مشيرةً إلى إتاحة قنوات تواصل وآلية مخصصة لتلقي الشكاوى والاستفسارات من الأهالي والمجتمعات المحلية عبر الرقم (+961 76 399 882) أو الخط الساخن للوزارة.</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:13:45.513906+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>كرامي من اجتماع الشركاء: إعادة الإعمار والتعافي التعليمي خطوتان متوازيتان نحو "رؤية 2040"</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D9%83%D8%B1%D8%A7%D9%85%D9%8A-%D9%85%D9%86-%D8%A7%D8%AC%D8%AA%D9%85%D8%A7%D8%B9-%D8%A7%D9%84%D8%B4%D8%B1%D9%83%D8%A7%D8%A1-%D8%A5%D8%B9%D8%A7%D8%AF%D8%A9-%D8%A7%D9%84%D8%A5%D8%B9%D9%85%D8%A7%D8%B1-%D9%88%D8%A7%D9%84%D8%AA%D8%B9%D8%A7%D9%81%D9%8A-%D8%A7%D9%84%D8%AA%D8%B9%D9%84%D9%8A%D9%85%D9%8A-%D8%AE%D8%B7%D9%88%D8%AA%D8%A7%D9%86-%D9%85%D8%AA%D9%88%D8%A7%D8%B2%D9%8A%D8%AA%D8%A7%D9%86-%D9%86%D8%AD%D9%88-%D8%B1%D8%A4%D9%8A%D8%A9</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>كرامي من اجتماع الشركاء: إعادة الإعمار والتعافي التعليمي خطوتان متوازيتان نحو "رؤية 2040"
+ترأست وزيرة التربية والتعليم العالي الدكتورة ريما كرامي اجتماعا للجمعيات الشريكة مع الوزارة في خطة الإستجابة الوطنية لقطاع التربية والتعليم، في حضور المدير العام للتربية الأستاذ فادي يرق ، ومديرة الإرشاد والتوجيه الدكتورة هيلدا الخوري ، وممثلين عن المنظمات الدولية الشريكة والجمعيات التي تعمل على الأرض .
+بعد النشيد الوطني وتقديم من المنسقة إديت خليفة ، عرض ضابط الإرتكاز في الوزارة ومسؤول التعليم غير النظامي جوليان جلخ تتقريرا عن تأثير الحرب على القطاع التربوي وتحول عدد كبير من المدارس إلى مراكز للإيواء ، وأشار إلى خطة الوزارة التي ركزت على تأمين استمرارية التعليم على الرغم من المدارس المتضررة على مستويات عدة بين أضرار خفيفة ومتوسطة وكبيرة مثل المدارس المهدمة .
+وتحدث عن استراتيجية الوزارة في ظل عودة عدد كبير من النازحين إلى سوريا . وتحدث عن أنواع الإستجابة من خلال التعليم النظامي والتعليم غير النظامي ، وبالتالي أنواع التقييم ، وقياس الفجوات والفاقد التعليمي .
+كذلك تحدث ممثلون عن اليونيسف ومنظمة غوث الأولاد عن حاجات القطاع التربوي بناء على رؤية الوزارة 2040 ، وتعزيز طرق الوصول إلى التعليم ، وتدريب الطواقم الوطنية بالتعاون مع الشركاء.
+الوزيرة :
+ثم تحدثت الوزيرة كرامي فشكرت جميع الشركاء على جهودهم،
+وقالت :
+نلتقي في لحظة حرجة للتعليم في لبنان. فبعد حرب مدمرة أخرى، تواجه مدارسنا ومعلمونا وأطفالنا وعائلاتنا تحديات هائلة. ومنذ آذار/مارس، تضررت 436 منشأة تعليمية ودُمرت 39 منشأة أخرى. كما استُشهد أو جُرح معلمون. وهناك نحو مئة ألف متعلم في المناطق المتضررة من الحرب لم يتمكنوا من العودة إلى مدارسهم.
+لكنكم لم تتراجعوا، بل تقدمتم إلى الأمام. فمن خلال خطة الاستجابة للبنان، والنداءات العاجلة، وملحق عام 2026، وقف إلى جانب وزارة التربية والتعليم العالي. وتتقدم اليوم خمس وسبعون منظمة بطلبات دعم من خلال خطة الاستجابة للبنان لعام 2027. لقد وقفتم معنا في استراتيجية العودة، واحترمتم مبدأً أعتز به بشدة: رؤية واحدة تحت مظلة وزارة التربية والتعليم العالي. الوزارة تقود، وهي التي تحدد الأولويات والمعايير. وقد اخترتم اتباع تلك القيادة، سواء على الأرض أو في هذه القاعة.
+وباسم الوزارة، أتوجه إليكم بالشكر. وإلى المعلمين ومديري المدارس وموظفي الشركاء الداعمين الذين حافظوا على استمرارية التعلم داخل الصفوف، وفي مراكز الإيواء، ومحطات التعليم والتعلم، ومراكز الشراكة: إننا نرى عملكم ونقدره حق التقدير.
+وأضافت الوزيرة : لدينا اليوم صورة أكثر وضوحاً؛ إذ يظهر تقييم أثر الحرب، والتقييم التشخيصي الوطني، ونتائج برنامج التقييم الدولي للطلاب (بيزا) تداعيات الحرب وفجوات التعلم الأساسية في نظامنا التعليمي الرسمي، والتي كان الكثير منها موجوداً قبل الحرب وأصبح الآن أكثر إلحاحاً. ومعاً، تؤدي بنا هذه المؤشرات إلى استنتاج أساسي واحد: يجب ألا نستعيد مدارسنا فحسب، بل يجب أن نستعيد التعلم نفسه.
+ومن هنا يجب أن ننتقل من الأدلة إلى العمل، إذ تركز "رؤية 2040" الصادرة عن وزارة التربية والتعليم العالي على تحويل البيئة التعليمية للمتعلم في الفترة الممتدة من 2025 إلى 2040. وهي تتضمن سبعة مجالات: البنية التحتية المنصفة، والموارد، والوصول الرقمي؛ والتميز في التعليم والتعلم؛ ورفاه المتعلم، وحمايته، وصحته، ودعمه النفسي والاجتماعي؛ والقيادة التشاركية لتحسين التعلم؛ وشراكة الأهالي والأدوار المنسقة لدعم التعلم؛ والشراكة مع المجتمع المحلي والشتات؛ والبحث العلمي والشراكات المهنية لبناء القدرات.
+وقد حولنا هذه الرؤية للعام الدراسي الحالي إلى أهداف استراتيجية، بدءاً من التعليم والتعلم للجميع وصولاً إلى التماسك الاجتماعي والرفاه.
+وقالت : المدرسة المُرممة ليست بالضرورة مدرسة عاملة، والمدرسة العاملة ليست بالضرورة مدرسة يتعلم فيها الأطفال. ولهذا السبب، يجب أن تسير إعادة التأهيل والتعافي التشغيلي جنباً إلى جنب، استرشاداً بأولويات واضحة، وإجراءات مشتركة، ومراقبة شفافة.
+الاستجابة للطوارئ ليست التفافاً على الرؤية، بل هي الميل الأول على الطريق. فالمدرسة التي تُعاد فتحها بأمان، والطفل الذي يعود إلى التعلم، والمعلم الذي يتلقى دعماً نفسياً واجتماعياً: كل خطوة من هذه الخطوات تُعد خطوة نحو عام 2040، إذا خططنا لها على هذا النحو.
+وختمت الوزيرة: لا يقيس أطفالنا الوقت بدورات المشاريع، بل يقيسونه بالسنوات الدراسية، وكل سنة منها ثمينة. لذا، دعونا لا نقيس نجاحنا بعدد المدارس التي نعيد فتحها فحسب، بل بعدد الأطفال الذين يعودون إلى صفوف آمنة ويتعلمون حقاً.
+ثم أجابت مديرة الإرشاد والتوجيه الدكتورة هيلدا الخوري والمهندس خالد جوجو عن أسئلة الحضور حول تأهيل المدارس وتجهيزها لتأمين استمرارية التعليم ، وكذلك عن المدارس التي ما زالت مراكز للإيواء.</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:13:47.337554+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>الاهداف الإستراتيجية لوزارة التربية والتعليم العالي</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D8%A7%D9%84%D8%A7%D9%87%D8%AF%D8%A7%D9%81-%D8%A7%D9%84%D8%A5%D8%B3%D8%AA%D8%B1%D8%A7%D8%AA%D9%8A%D8%AC%D9%8A%D8%A9-%D9%84%D9%88%D8%B2%D8%A7%D8%B1%D8%A9-%D8%A7%D9%84%D8%AA%D8%B1%D8%A8%D9%8A%D8%A9-%D9%88%D8%A7%D9%84%D8%AA%D8%B9%D9%84%D9%8A%D9%85-%D8%A7%D9%84%D8%B9%D8%A7%D9%84%D9%8A</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>لأي إستفسار الإتصال على:
+٠١/٧٧٢٠٠٠
+الرئيسية
+حول الوزارة
+الوزيرة
+الهيكلية التنظيمية
+المهمة
+التاريخ القانوني
+الوزراء السابقون
+البيان الوزاري
+روابط
+المركز الإعلامي
+الأخبار
+الأحداث
+معرض الصور
+معرض الفيديو
+تعاميم، مذكرات، قرارات، إعلانات
+خدمات
+إعلانات
+استدراج عروض ومناقصات
+ترشيحات ومنح
+مسابقات
+وظائف
+روابط هامة
+البرامج والمشاريع
+دورات تدريبية عبر الإنترنت
+خدمات الكترونية
+الزاوية الثقافية
+مسابقات وانشطة علمية
+مسابقات وانشطة أدبية
+مسابقات وانشطة فنية
+نتائج واحتفالات
+تواصل معنا
+إتصل بنا
+مكاتبنا
+Our Partners
+Breadcrumb
+الرئيسية
+المركز الإعلامي
+الأخبار
+الاهداف الإستراتيجية لوزارة التربية والتعليم العالي
+الاهداف الإستراتيجية لوزارة التربية والتعليم العالي
+الوزير
+8-10-2026
+معرض الصور</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:13:49.318618+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>المكتب الإعلامي لوزيرة التربية والتعليم العالي: التعليم الحضوري خيار مرتبط بواقع كل مدرسة وبشروط السلامة العامة</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D8%A7%D9%84%D9%85%D9%83%D8%AA%D8%A8-%D8%A7%D9%84%D8%A5%D8%B9%D9%84%D8%A7%D9%85%D9%8A-%D9%84%D9%88%D8%B2%D9%8A%D8%B1%D8%A9-%D8%A7%D9%84%D8%AA%D8%B1%D8%A8%D9%8A%D8%A9-%D9%88%D8%A7%D9%84%D8%AA%D8%B9%D9%84%D9%8A%D9%85-%D8%A7%D9%84%D8%B9%D8%A7%D9%84%D9%8A-%D8%A7%D9%84%D8%AA%D8%B9%D9%84%D9%8A%D9%85-%D8%A7%D9%84%D8%AD%D8%B6%D9%88%D8%B1%D9%8A-%D8%AE%D9%8A%D8%A7%D8%B1-%D9%85%D8%B1%D8%AA%D8%A8%D8%B7-%D8%A8%D9%88%D8%A7%D9%82%D8%B9</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>المكتب الإعلامي لوزيرة التربية والتعليم العالي: التعليم الحضوري خيار مرتبط بواقع كل مدرسة وبشروط السلامة العامة
+ردّ المكتب الإعلامي لوزيرة التربية والتعليم العالي الدكتورة ريما كرامي على ما أثارته النائب بولا يعقوبيان حول تصنيف إحدى المدارس في قضاء بنت جبيل ضمن المدارس التي يمكن أن تعتمد التعليم الحضوري،على الرغم من كونها متضررة وقريبة من مواقع الاحتلال ,متهمة الوزراة بالعشوائية في القرارات ووضع سلامة الطلاب والمعلمين على المحك.وجاء في الرد : 
+يهم المكتب الإعلامي التأكيد على أن الجداول التي تتضمن أسماء المدارس والثانويات تأتي في إطار تحديد الخيارات التعليمية المتاحة وفاقا للواقع الأمني، ولا تعني أن التعليم الحضوري مفروض بصورة جامدة أو بمعزل عن التطورات الميدانية ,وأن هذا الجدول يتم تعديله يوميا بحسب التطورات الأمنية والتحديثات المتعلقة بمراكز الايواء.
+ويؤكد المكتب الاعلامي أن القرار رقم 1241 الصادر عن وزارة التربية ينص بوضوح على أن "يعتمد التعليم الحضوري خياراً أول كلما توافرت شروط السلامة العامة والقدرة التشغيلية المناسبة. وعند تعذّر التعليم الحضوري كلياً أو جزئياً، يمكن اعتماد التعليم المدمج أو التعليم من بُعد بصورة موقتة".
+ويؤكد المكتب الاعلامي ان مديري المدارس والثانويات الرسمية على اطلاع كامل بهذه المعطيات والتعليمات وآلية تطبيقها، وهم معنيون بتقدير الموقف على الأرض، بالتنسيق مع الأهل وفعاليات البلدات والجهات المحلية، واختيار الصيغة التعليمية التي يرونها أكثر ملاءمة وأماناً للطلاب والهيئات التعليمية وابلاغ الوزراة التي بدورها ستقوم بتسهيل كل ما يلزم لمساعدتهم في إطار المرونة المعتمدة من جانبها.
+اشارة الى ان المدرسة التي اشارت اليها سعادة النائب قد وردت ضمن التعليم الحضوري عن طريق خطأ مطبعي في الجدول.مع العلم انها من ضمن تجمع مدرسي خاضع للخيار المتاح وفاقا للواقع الأمني, وقد تم تصحيحه فورا.</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:13:58.511442+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>التعليم في لبنان تحت تأثير الحرب… تقرير "أثر الحرب على قطاع التعليم في لبنان ٢٠٢٦"</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D8%A7%D9%84%D8%AA%D8%B9%D9%84%D9%8A%D9%85-%D9%81%D9%8A-%D9%84%D8%A8%D9%86%D8%A7%D9%86-%D8%AA%D8%AD%D8%AA-%D8%AA%D8%A3%D8%AB%D9%8A%D8%B1-%D8%A7%D9%84%D8%AD%D8%B1%D8%A8%E2%80%A6-%D8%AA%D9%82%D8%B1%D9%8A%D8%B1-%D8%A3%D8%AB%D8%B1-%D8%A7%D9%84%D8%AD%D8%B1%D8%A8-%D8%B9%D9%84%D9%89-%D9%82%D8%B7%D8%A7%D8%B9-%D8%A7%D9%84%D8%AA%D8%B9%D9%84%D9%8A%D9%85-%D9%81%D9%8A-%D9%84%D8%A8%D9%86%D8%A7%D9%86-%D9%A2%D9%A0%D9%A2%D9%A6</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>لأي إستفسار الإتصال على:
+٠١/٧٧٢٠٠٠
+الرئيسية
+حول الوزارة
+الوزيرة
+الهيكلية التنظيمية
+المهمة
+التاريخ القانوني
+الوزراء السابقون
+البيان الوزاري
+روابط
+المركز الإعلامي
+الأخبار
+الأحداث
+معرض الصور
+معرض الفيديو
+تعاميم، مذكرات، قرارات، إعلانات
+خدمات
+إعلانات
+استدراج عروض ومناقصات
+ترشيحات ومنح
+مسابقات
+وظائف
+روابط هامة
+البرامج والمشاريع
+دورات تدريبية عبر الإنترنت
+خدمات الكترونية
+الزاوية الثقافية
+مسابقات وانشطة علمية
+مسابقات وانشطة أدبية
+مسابقات وانشطة فنية
+نتائج واحتفالات
+تواصل معنا
+إتصل بنا
+مكاتبنا
+Our Partners
+Breadcrumb
+الرئيسية
+المركز الإعلامي
+الأخبار
+التعليم في لبنان تحت تأثير الحرب… تقرير "أثر الحرب على قطاع التعليم في لبنان ٢٠٢٦"
+التعليم في لبنان تحت تأثير الحرب… تقرير "أثر الحرب على قطاع التعليم في لبنان ٢٠٢٦"
+الوزير
+9-09-2026
+المرفقات
+Attacks_on_Education_110926_e-version (2).pdf
+(906.51 KB)</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:01.593702+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>وزيرة التربية والتعليم العالي تطلع على التجربة الأردنية في الاعتماد وضمان الجودة وتبحث سبل التعاون المشترك</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D9%88%D8%B2%D9%8A%D8%B1%D8%A9-%D8%A7%D9%84%D8%AA%D8%B1%D8%A8%D9%8A%D8%A9-%D9%88%D8%A7%D9%84%D8%AA%D8%B9%D9%84%D9%8A%D9%85-%D8%A7%D9%84%D8%B9%D8%A7%D9%84%D9%8A-%D8%AA%D8%B7%D9%84%D8%B9-%D8%B9%D9%84%D9%89-%D8%A7%D9%84%D8%AA%D8%AC%D8%B1%D8%A8%D8%A9-%D8%A7%D9%84%D8%A3%D8%B1%D8%AF%D9%86%D9%8A%D8%A9-%D9%81%D9%8A-%D8%A7%D9%84%D8%A7%D8%B9%D8%AA%D9%85%D8%A7%D8%AF-%D9%88%D8%B6%D9%85%D8%A7%D9%86-%D8%A7%D9%84%D8%AC%D9%88%D8%AF%D8%A9</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>وزيرة التربية والتعليم العالي تطلع على التجربة الأردنية في الاعتماد وضمان الجودة وتبحث سبل التعاون المشترك
+في إطار برنامج زيارتها الرسمية إلى الأردن ، اطّلعت وزيرة التربية والتعليم العالي الدكتورة ريما كرامي، والوفد المرافق لها على التجربة الأردنية في مجال الاعتماد وضمان الجودة، ومسيرة تطور منظومة الاعتماد وآليات عمل هيئة الاعتماد وضمان الجودة.
+وذلك في خلال زيارتها مقر الهيئة ولقائها رئيسها، الدكتور ظافر الصرايرة في حضور نائب رئيس الهيئة الدكتور سعد بني محمد، وعدد من مديري المديريات والمختصين في الهيئة.
+واستعرض الصرايرة نشأة منظومة الاعتماد وضمان الجودة في الأردن، مبينًا أنها بدأت مع التوسع في التعليم العالي الخاص، وتطورت عبر أطر تشريعية متعاقبة حتى إنشاء هيئة مستقلة للاعتماد وضمان الجودة، مشيراً إلى أن المنظومة شهدت مؤخرًا توسعًا في اختصاصاتها بدمج هيئة تنمية وتطوير المهارات المهنية والتقنية معها، لتشمل التعليم والتدريب المهني والتقني إلى جانب التعليم العالي.
+وأوضح أن المنظومة انتقلت من التركيز على المتطلبات الكمية، كأعداد الطلبة والمدرّسين والمساحات والتجهيزات، إلى منظومة أكثر شمولًا تُعنى بجودة العملية التعليمية ومخرجاتها وأثرها، مع متابعة مستمرة.
+وأشار إلى أن الهيئة تعمل على تطوير معايير تواكب تكنولوجيا المعلومات والأمن السيبراني والذكاء الاصطناعي بالتعاون مع القطاع الخاص، بما يسهم في مواءمة البرامج مع سوق العمل، وأن معايير الاعتماد تخضع لمراجعة مستمرة لمواكبة المستجدات العلمية والتكنولوجية.
+من جانبها، أشادت الدكتورة كرامي بالتجربة الأردنية في مجال الاعتماد وضمان الجودة، مؤكدة أهمية تبادل الخبرات بين هيئات ومؤسسات ضمان الجودة العربية، والاستفادة من التجارب المختلفة مع مراعاة الخصوصية الثقافية والاجتماعية لكل دولة، وعدم النقل الحرفي للنماذج الخارجية دون تكييفها مع السياق المحلي.
+وشددت على أهمية إشراك أصحاب العمل والممارسين والخبرات المهنية في تطوير البرامج الأكاديمية ومعايير الجودة، وربط مخرجات التعليم باحتياجات سوق العمل، والتوسع في التدريب العملي للطلبة، والاستفادة من الخبرات المهنية إلى جانب الأكاديمية في العملية التعليمية.
+كما تناولت أهمية تعزيز البحث العلمي والنشر الأكاديمي وبناء القدرات المؤسسية، بما يسهم في تطوير البرامج والخطط الدراسية ومعايير الاعتماد بصورة أكثر ارتباطًا بالواقع واحتياجات التنمية.
+وبحث الجانبان سبل تعزيز التعاون بين الأردن ولبنان في مجالات الاعتماد وضمان الجودة، وتبادل الخبرات والدراسات والممارسات الفضلى، وتفعيل التواصل المباشر بين المختصين واللجان الفنية، وتنظيم اللقاءات والزيارات الفنية، إلى جانب دعم التعاون الأكاديمي وتبادل الطلبة وأعضاء هيئة التدريس، والاستفادة من اللقاءات عن بُعد في متابعة الملفات الفنية وتبادل المعرفة.
+وأكد الجانبان أهمية بناء قنوات اتصال مباشرة بين المؤسسات والجهات المعنية، وتحديد نقاط اتصال فنية تسهم في تسريع تبادل المعلومات والخبرات ومتابعة مجالات التعاون، بما يعزز الاستفادة المتبادلة من التجربتين الأردنية واللبنانية في تطوير منظومات التعليم والاعتماد وضمان الجودة.</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:08.651072+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>الوزيرة كرامي تطلع على التجارب الأردنية في التدريب الإداري وتطوير المناهج وبناء قدرات المعلمين</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D8%A7%D9%84%D9%88%D8%B2%D9%8A%D8%B1%D8%A9-%D9%83%D8%B1%D8%A7%D9%85%D9%8A-%D8%AA%D8%B7%D9%84%D8%B9-%D8%B9%D9%84%D9%89-%D8%A7%D9%84%D8%AA%D8%AC%D8%A7%D8%B1%D8%A8-%D8%A7%D9%84%D8%A3%D8%B1%D8%AF%D9%86%D9%8A%D8%A9-%D9%81%D9%8A-%D8%A7%D9%84%D8%AA%D8%AF%D8%B1%D9%8A%D8%A8-%D8%A7%D9%84%D8%A5%D8%AF%D8%A7%D8%B1%D9%8A-%D9%88%D8%AA%D8%B7%D9%88%D9%8A%D8%B1-%D8%A7%D9%84%D9%85%D9%86%D8%A7%D9%87%D8%AC-%D9%88%D8%A8%D9%86%D8%A7%D8%A1</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>الوزيرة كرامي تطلع على التجارب الأردنية في التدريب الإداري وتطوير المناهج وبناء قدرات المعلمين
+تابعت وزيرة التربية والتعليم العالي الدكتورة ريما كرامي برنامج زيارتها الرسمية إلى الأردن ، وزارت الأكاديمية الأردنية للإدارة الحكومية حيث اجتمعت والوفد المرافق مع مدير برامج التدريب الجديدة الدكتور مصطفى حمارنة ، و كانت فرصة مهمة للبحث في آليات التعاون خصوصا وان لدى هذه الاكاديمية تجربة متقدمة في التدريب الإداري و بناء القدرات . وفي خلال اللقاء تم التطرق الى تجربة الأردن في التطوير الإداري و التشبيك المؤسسي و خطوات التطبيق العملية.
+وانتقلت الوزيرة كرامي والوفد الى أكاديمية الملكة رانيا لتدريب المعلمين واجتمعت مع المدير التنفيذي للأكاديمية عبد المجيد شملاوي وفريق عمل الأكاديمية ، وتضمن الاجتماع عرضاً للسياق التاريخي للأكاديمية ودورها الريادي في تطوير التعليم، تلاه استعراض لـ *مسارات التطوير المهني المتكامل* التي تعتمدها. 
+وشكّلت الزيارة فرصة للتعرّف عن قرب على تجربة الأكاديمية ونموذجها في تمكين المعلمين والتربويين وتطوير قدراتهم،كما اطلعت الوزيرة على *آلية عمل الأكاديمية في تصميم البرامج التدريبية وتنفيذها*، والتي تشمل المعلمين والمديرين والمشرفين التربويين، بما يضمن بناء قدرات الكوادر التعليمية والإدارية وفاقا لأحدث المعايير المحلية والدولية. 
+ثم انتقلت الوزيرة والوفد إلى المجلس الأعلى للمناهج حيث اجتمعت مع رئس المجلس الأعلى في المجلس الوطني لتطوير المناهج الدكتور محي الدين توق ، وكان عرض لورشة تطوير المناهج التربوية في لبنان ومسار تطوير المناهج في الأردن ونقاط التقاطع بينهما وادخال الذكاء الاصطناعي كوسيلة لتعزيز وسائل البحث واستخراج المؤشرات في عملية التطوير المستمر .</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:11.609862+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>وزيرة التربية تبدأ زيارة رسمية للأردن لتفعيل التعاون التعليمي وتشكيل لجان فنية مشتركة</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D9%88%D8%B2%D9%8A%D8%B1%D8%A9-%D8%A7%D9%84%D8%AA%D8%B1%D8%A8%D9%8A%D8%A9-%D8%AA%D8%A8%D8%AF%D8%A3-%D8%B2%D9%8A%D8%A7%D8%B1%D8%A9-%D8%B1%D8%B3%D9%85%D9%8A%D8%A9-%D9%84%D9%84%D8%A3%D8%B1%D8%AF%D9%86-%D9%84%D8%AA%D9%81%D8%B9%D9%8A%D9%84-%D8%A7%D9%84%D8%AA%D8%B9%D8%A7%D9%88%D9%86-%D8%A7%D9%84%D8%AA%D8%B9%D9%84%D9%8A%D9%85%D9%8A-%D9%88%D8%AA%D8%B4%D9%83%D9%8A%D9%84-%D9%84%D8%AC%D8%A7%D9%86-%D9%81%D9%86%D9%8A%D8%A9</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>وزيرة التربية تبدأ زيارة رسمية للأردن لتفعيل التعاون التعليمي وتشكيل لجان فنية مشتركة
+بدأت وزيرة التربية والتعليم العالي الدكتورة ريما كرامي برنامج زيارتها الرسمية إلى المملكة الأردنية الهاشمية، ترافقها مديرة مكتبها مايا مداح وأمين سر مكتب الوزيرة جمال عبدو ، وكانت في استقبالها سفيرة لبنان لدى المملكة بريجيت طوق والأمين العام لوزارة التربية والتعليم الأردنية الدكتور نواف عجارمة . 
+تأتي هذه الزيارة انطلاقاً من اتفاقية التعاون الموقعة بين الحكومة اللبنانية ومجلس الوزراء الاردني ومن ضمنها وزارة التربية والتعليم العالي اللبنانية ووزارة التربية و التعليم وتنمية الموارد البشرية في المملكة الأردنية الهاشمية. وتهدف لتفعيل هذه الاتفاقية من خلال الاجتماع مع الجهات المعنية ووضع خطط عمل تنفيذية والى استثمار
+واقع لبنان والأردن الذين تجمعهما جغرافيا واحدة، ولغة واحدة، وتحديات تربوية مشتركة. ومن هنا، فإن تبادل الخبرات والتشبيك بين المؤسسات التربوية 
+للبلدين يعتبر أساسيا لما فيه خير البلدين. 
+المحطة الأولى في برنامج الزيارة كانت في وزارة التربية والتعليم حيث استقبلها والوفد المرافق وزير التربية والتعليم وتنمية الموارد البشرية الدكتور عزمي محافظة ، وتركز البحث على تعزيز العلاقات التربوية والجامعية بين البلدين. 
+وعبرت الوزيرة عن شكرها وتقديرها للحفاوة في الاستقبال وانفتاح الوزير على التعاون مع وزارة التربية والتعليم العالي في لبنان . ووجهت التحية عبر الوزير إلى جلالة ملك الأردن عبد الله الثاني وحكومته على الوقوف إلى جانب لبنان في أصعب الظروف . 
+الوزير الأردني رحب بالوزيرة والوفد المرافق مشيرا إلى ان الوزارتين تعملان معا لكل ما يوفر آفاقا للتطور العلمي والتكنولوجي وتنمية الموارد البشرية في البلدين .وتوافق الجانبان على تفعيل البرنامج التنفيذي عبر الترتيب الآتي :
+أولا: تشكيل لجان فنية مشتركة من الجانبين للتعاون في مجلات محددة بحيث يتم عقد اللقاءات عبر تقنيات الاتصال المرئي لمتابعة التخطيط لتنفيذ البرامج والأفكار المطروحة لجهة تطوير المناهج وتبادل الخبرات في مجال بناء قدرات مديري المدارس إذ عرض الجانبان تجربتهما في هذا المجال . 
+وتم التفاق على تنظيم ملتقى مشترك يجمع المسؤولين عن مراكز المناهج والتدريب ورؤساء الجامعات والخبراء من الأردن ولبنان، بهدف تبادل الرؤى وتطوير حلول عملية للتحديات المشتركة، خصوصا لجهة استغلال الموارد المتاحة والاستجابة للأزمات.
+وتطرق المجتمعون إلى طلب سفيرة لبنان في الأردن تحويل عدد من المنح إلى طلبة البكالوريوس وإرسال الجانب اللبناني خطابا رسميا لتحويل عدد من المنح المنصوص عليها في البرنامج التنفيذي للتعاون في مجال التعليم العالي للسنوات 2010 2012 إلى درجة البكالوريوس بدل الماجستير والدكتوراه
+وعرض المجتمعون أيضا التعاون في مجال التعليم المهني وذلك بعرض الموضوع في خلال اجتماعات اللجان المشتركة التي تعقد كل سنتين عن طريق وزارة الصناعة والتجارة الاردنية و وزارة الاقتصاد اللبنانية
+وتم التوافق ايضا على الاستفادة من تجربة الجانب اللبناني في توقيع مذكرات تفاهم مع جامعات لتوظيف الأبحاث والدراسات لفائدة وزارة التربية والتعليم العالي في لبنان
+واقر المجتمعون تسمية نقاط اتصال من الوزارتين لاستكمال التشاور والتنسيق ومتابعة تفعيل وتنفيذ البرنامج التنفيذي.</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:13.627115+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>الوزيرة</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D8%A7%D9%84%D9%88%D8%B2%D9%8A%D8%B1%D8%A9</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>لأي إستفسار الإتصال على: ٠١/٧٧٢٠٠٠
+أصدرت وزيرة التربية والتعليم العالي الدكتورة ريما كرامي القـرار رقـم 1188/م/2026 حول تحديد مواعيد امتحانات الكولوكيوم للعام 2026 - الدورة الثانية
+للاطلاع على الجدول يرجى تحميل المرفقات</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:15.453829+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>وزارة التربية تكرم نخبة من معلّمي المدرسة الرسمية ضمن مبادرة "المعلم الملهم"</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D9%88%D8%B2%D8%A7%D8%B1%D8%A9-%D8%A7%D9%84%D8%AA%D8%B1%D8%A8%D9%8A%D8%A9-%D8%AA%D9%83%D8%B1%D9%85-%D9%86%D8%AE%D8%A8%D8%A9-%D9%85%D9%86-%D9%85%D8%B9%D9%84%D9%91%D9%85%D9%8A-%D8%A7%D9%84%D9%85%D8%AF%D8%B1%D8%B3%D8%A9-%D8%A7%D9%84%D8%B1%D8%B3%D9%85%D9%8A%D8%A9-%D8%B6%D9%85%D9%86-%D9%85%D8%A8%D8%A7%D8%AF%D8%B1%D8%A9-%D8%A7%D9%84%D9%85%D8%B9%D9%84%D9%85-%D8%A7%D9%84%D9%85%D9%84%D9%87%D9%85</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>وزارة التربية تكرم نخبة من معلّمي المدرسة الرسمية ضمن مبادرة "المعلم الملهم"
+رعت وزيرة التربية والتعليم العالي الدكتورة ريما كرامي مبادرة المعلم المبدع وذلك في احتفال أقيم في قاعة المسرح في الوزارة في حضور المدير العام للتربية الأستاذ فادي يرق ورؤساء الوحدات المعنية ، رئيسة المركز التربوي للبحوث والإنماء البروفسورة هيام إسحق وجمع من المعلمين المبدعين الذين رشحتهم إدارات مدارسهم وثانوياتهم الرسمية بحسب سلسلة من المعايير والمسيرة المهنية وخصوصا التأثير الذي يتركه المعلم المبدع في المتعلمين .
+بعد النشيد الوطني ونشيد المدرسة الرسمية تحدثت منسقة المشروع الدكتورة ثناء الحلوة فعرضت على الشاشة الأصول المتبعة للاختيار بحسب كل محافظة وركزت على أهمية المعلم الذي يعطي من ذاته وتجربته وشخصيته فيشكل نموذجا وقدوة يحتذى بهما بين التلاميذ وفي المجتمع .
+الوزيرة :
+بعد ذلك تحدثت الوزيرة كرامي فقالت :
+نجتمع اليوم في مناسبة خاصة… فاليوم لا نحتفل بتقاعد معلم، ولا بتخرج طالب، ولا بإعلان نتائج امتحانات مدرسية أو رسمية.
+اليوم نحتفل بشيء لا يدخل عادة في الاحتفالات التربوية التقليدية… نحتفل بالأثر.
+بالأثر الذي يتركه معلم في حياة طلابه، وبالكلمة التي قد تغيّر مستقبل إنسان،
+وبالثقة التي يمنحها معلم لتلميذ فيكتشف من خلالها قدراته، وبالشغف الذي يوقظه داخل الصف، فيجعل التعلم تجربة تُعاش، لا مادة تُحفظ. ولهذا اخترنا أن تحمل هذه المبادرة اسم “المعلم الملهم”.
+ولعل أهم ما في هذه المبادرة أنها تجسد ما نؤمن به في وزارة التربية والتعليم العالي. فعندما نتحدث عن إصلاح التعليم، ينصرف التفكير غالباً إلى المناهج، أو التكنولوجيا، أو الأبنية، أو التمويل. وكلها عناصر أساسية، لكن أي إصلاح حقيقي لا يبدأ بها، بل يبدأ بالثقة بالمعلم، وتمكينه، والإيمان بأنه القادر على تحويل كل رؤية تربوية إلى واقع داخل الصف.
+فكل منهج جديد، وكل سياسة تربوية، وكل مشروع تطوير، لن يصبح واقعاً داخل الصف إذا لم يجد معلماً يؤمن به، ويمنحه الحياة، ويحوّل التعلم إلى تجربة قادرة على تغيير الإنسان.
+واخترنا هذه التسمية لنحتفي بأثر معلمينا لأننا نؤمن أن التعليم لا يبدأ بالمعلومة، بل بالقدرة على إلهام الإنسان ليبحث عنها. وأن أعظم المعلمين ليسوا أولئك الذين يملؤون دفاتر طلابهم، بل الذين يفتحون عقولهم، ويوقظون فضولهم، ويزرعون فيهم الثقة بأنفسهم وبقدرتهم على التعلم.
+بالنسبة لنا، المعلم الملهم هو ذاك الذي يرى في الطالب ما لم يره الطالب بعد في نفسه. يكتشف فيه إمكانات لم يكن يعرفها، ويفتح أمامه آفاقاً لم يكن يتخيلها، ويمنحه الثقة ليؤمن بأنه قادر على أن يصبح أفضل مما كان يظن. وحين يغيّر المعلم صورة الطالب عن نفسه، فإنه قد يغيّر مسار حياة كاملة.
+يقول الشاعر والفيلسوف وليم بتلر ييتس:
+“التعليم ليس ملء وعاء، بل إشعال نار.”
+وأنتم…معلمونا الملهمون… أشعلتم تلك النار.
+أشعلتم حب المعرفة، وفضول الاكتشاف، وروح المبادرة، والإيمان بأن المستقبل يمكن أن يكون أجمل مهما اشتدت التحديات.
+بالإضافة إلى ما ذكرته، فإني اؤمن ان المعلم الملهم هو أيضاً من يقود التجديد داخل مدرسته.
+فلا يكتفي بتكرار ما اعتاد عليه، بل يواصل التعلم، ويجرّب، ويطوّر ممارساته، ويبحث دائماً عن طرق تجعل التعلم أكثر معنى، وأكثر ارتباطاً بحياة الطلاب، وأكثر قدرة على إعدادهم للمستقبل.
+لكن التجديد الحقيقي في التعليم لا يحدث لأننا نطلب من المعلمين أن يتغيروا، بل لأنه يُتاح لهم أن يقودوا هم هذا التغيير. فالمعلم ليس منفذاً للإصلاح، بل شريك في صناعته، وحين نثق بمعلمينا، ونمنحهم المساحة ليبدعوا ويبتكروا ويجددوا، يصبح الإصلاح ممارسة يومية داخل كل صف، لا مجرد سياسة أو وثيقة.
+فالإلهام والتطوير ليسا مسارين منفصلين، بل إن كلاً منهما يغذي الآخر. فالمعلم الذي يلهم طلابه هو نفسه الذي لا يتوقف عن تطوير نفسه، والمعلم الذي يواصل التعلم هو الأقدر على أن يوقظ في طلابه حب التعلم.
+لقد أردنا من خلال هذه المبادرة أن نقول شيئاً بسيطاً، لكنه بالغ الأهمية:
+إن المدرسة الرسمية مليئة بقصص النجاح التي لا يعرفها كثيرون، وبمعلمين يعملون بصمت، ويتركون كل يوم أثراً عميقاً في حياة طلابهم، من دون أن يطلبوا تقديراً أو ينتظروا تكريماً.
+وكان من واجبنا أن نبدأ بتسليط الضوء على بعض هذه النماذج، لأنها تمثل الوجه الحقيقي للمدرسة الرسمية، ولأن المدرسة الرسمية ليست مجرد مؤسسة تعليمية، بل هي واحدة من أهم مؤسسات الدولة، تحمل رسالة بناء الإنسان، وتصون مبدأ تكافؤ الفرص، وتجمع أبناء وبنات هذا الوطن على اختلافهم حول حق واحد هو حقهم في التعلم.
+وأود أن أتوجه بالشكر إلى مدراء المدارس والثانويات الرسمية في الحملة الوطنية لدعم المدرسة الرسمية ، لأنهم كانوا شركاء حقيقيين في هذه المبادرة.
+فقد طلبنا منهم ألا يبحثوا عن المعلم الأكثر شهرة، ولا عن صاحب أعلى النتائج، بل عن المعلم الذي ترك أثراً لا يُنسى، وغيّر حياة طالب، أو أعاد إليه ثقته بنفسه، أو جعل المدرسة مكاناً يشعر فيه الطلاب بالأمان، والانتماء، والشغف بالتعلم.
+وقد كانت القصص التي وصلت إلينا مؤثرة بحق، وأكدت أن مدارسنا الرسمية تختزن ثروة بشرية نفتخر بها جميعاً.
+إن هذا التكريم لا يضعكم في نهاية رحلة، بل في بدايتها.
+فهو يؤسس لثقافة تربوية تقودها مدارس الحملة الوطنية لدعم المدرسة الرسمية؛ ثقافة نريدها أن تكبر عاماً بعد عام؛ ثقافة تعتبر ان التربية ليست مهنة فحسب، بل علاقة إنسانية عميقة قد تغيّر مسار حياة كاملة.
+ثقافة ترى في الإلهام قيمة تربوية، وفي الأثر معياراً للتميز، وفي التجديد مسؤولية مهنية، وفي المعلم قائداً للتغيير، وصانعاً للمستقبل، قبل أن يكون ناقلاً للمعرفة.
+فقد ينسى الطالب درساً، وقد ينسى علامة، لكنه لا ينسى أبداً معلماً آمن به، وشجعه، ومنحه فرصة، ورأى فيه ما لم يكن يراه في نفسه.
+أيها المعلمون الملهمون،إن تكريمكم اليوم هو تكريم لكل معلم في المدرسة الرسمية يحمل رسالته بإخلاص، ويؤمن بأن بناء الإنسان هو أعظم استثمار يمكن أن يقدمه لوطنه.
+وهو أيضاً رسالة إلى المجتمع اللبناني بأن المدرسة الرسمية لا تختصر بما تواجهه من تحديات، بل بما تختزنه من طاقات، ومن رجال ونساء يصنعون مستقبل هذا الوطن كل يوم، داخل الصفوف، بصبر، وإبداع، وإيمان.
+لكنني أطمح أن يكون لهذه المبادرة معنى أبعد من التكريم نفسه.
+أطمح أن تصبح تقليداً وطنياً يعيد تعريف التميز في التعليم. تميزاً لا يقاس فقط بما ينجزه المعلم داخل الصف، بل بما يتركه في حياة طلابه، وبقدرته على اكتشاف إمكاناتهم، وإطلاق طاقاتهم، وقيادة التجديد، وبناء الثقة، وصناعة الأمل.
+فهذه هي الثقافة التربوية التي نريد أن نبنيها معاً. شكراً لكم… شكراً لأنكم أثبتم أن أجمل ما يتركه المعلم ليس ما يكتبه على اللوح، بل ما يكتبه في عقول طلابه، وفي ثقتهم بأنفسهم، وفي مسار حياتهم. وقد نبني مدرسة بالحجر، لكننا لا نبني أجيالاً إلا بالمعلم.
+مبارك لكم هذا التكريم. ومبارك للمدرسة الرسمية أن فيها معلمين يجعلوننا، كل يوم، أكثر إيماناً بأن مستقبل التعليم في لبنان سيبنيه أولئك الذين لا يكتفون بأن يعلّموا، بل يلهمون.
+ثم سلمت الوزيرة كرامي والمدير العام الأستاذ فادي يرق ومدير التعليم الأساسي جورج داوود ومدير التعليم الثانوي خالد فايد الدروع والشهادات على المعلمين المبدعين وتم أخذ الصور التذكارية في حضور مديري المدارس المشاركة .</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:17.285575+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>وزارة التربية تكرّم الفائزين في مسابقة «اليابان في عيون لبنانيّة»... لوحاتٌ تجسّد الحوار الثقافيّ بين لبنان واليابان</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://www.mehe.gov.lb/ar/media-center/news/%D9%88%D8%B2%D8%A7%D8%B1%D8%A9-%D8%A7%D9%84%D8%AA%D8%B1%D8%A8%D9%8A%D8%A9-%D8%AA%D9%83%D8%B1%D9%91%D9%85-%D8%A7%D9%84%D9%81%D8%A7%D8%A6%D8%B2%D9%8A%D9%86-%D9%81%D9%8A-%D9%85%D8%B3%D8%A7%D8%A8%D9%82%D8%A9-%C2%AB%D8%A7%D9%84%D9%8A%D8%A7%D8%A8%D8%A7%D9%86-%D9%81%D9%8A-%D8%B9%D9%8A%D9%88%D9%86-%D9%84%D8%A8%D9%86%D8%A7%D9%86%D9%8A%D9%91%D8%A9%C2%BB-%D9%84%D9%88%D8%AD%D8%A7%D8%AA%D9%8C-%D8%AA%D8%AC%D8%B3%D9%91%D8%AF</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>وزارة التربية تكرّم الفائزين في مسابقة «اليابان في عيون لبنانيّة»... لوحاتٌ تجسّد الحوار الثقافيّ بين لبنان واليابان
+كرّمت وزارة التربية والتعليم العالي الفائزين في مسابقة الرسم «اليابان في عيون لبنانيّة»، الّتي نظّمتها مصلحة الشؤون الثقافيّة والفنون الجميلة بالشّراكة مع جمعيّة «ليباجايكا»، وبدعم من السفارة اليابانيّة في لبنان، والوكالة اليابانيّة للتعاون الدّوليّ (JICA)، واستهدفت تلامذة الحلقة الثانية من مرحلة التعليم الأساسيّ، في إطار مبادرة تعزّز الحوار الثقافيّ وتفتح أمام التلامذة نافذة للتعرّف إلى الحضارة اليابانيّة والتّعبير عنها بلغة الفنّ.
+حضر الاحتفال المدير العام للتربية فادي يرق، وممثّلة السّفارة اليابانيّة في لبنان إيكومي أوغيواري، وممثّلة الوكالة اليابانيّة للتعاون الدّوليّ (JICA) زينة خلف، ورئيس جمعيّة «ليباجايكا» المهندس كمال مقداد وأعضاء الجمعيّة، ورئيسة مصلحة الشؤون الثقافيّة والفنون الجميلة صونيا الخوري، ورئيس دائرة التّعليم الإبتدائيّ هادي زلزلي، ورئيسة دائرة الفنون الجميلة في المصلحة هلا حمدان إلى جانب عدد من المسؤولين التربويّين ومديري المدارس والهيئات التعليميّة وأهالي التلامذة.
+وأكّد المدير العامّ للتربية، في كلمة ألقاها خلال الاحتفال، أنّ التربية تقوم على بناء الإنسان فكريًّا ووجدانيًّا وجماليًّا، وأنّ الفنون تشكّل ركيزة أساسيّة في تنمية شخصيّة المتعلّم، لما تؤدّيه من دور في صقل الإبداع وترسيخ قيم الحوار والانفتاح واحترام التنوّع الثقافيّ.
+كما أُلقيت كلمات لكلٍّ من ممثّلي السفارة اليابانيّة، والوكالة اليابانيّة للتعاون الدوليّ، وجمعيّة «ليباجايكا»، ومصلحة الشؤون الثقافيّة والفنون الجميلة، فأجمعت على أهمّيّة مواصلة التعاون الثقافيّ والتربويّ بين لبنان واليابان، وتعزيز المبادرات المشتركة الّتي تتيح للتلامذة اكتشاف ثقافات الشعوب، وتنمية مواهبهم، وترسيخ قيم التفاهم من خلال الفنّ والأنشطة الثقافيّة.
+ولفتت اللّوحات المشاركة أنظار الحاضرين بما عكسته من مستوى فنّيّ متميّز، إذ عبّر التلامذة، بأفكار مبتكرة ورؤى إبداعيّة، عن جوانب من الثقافة اليابانيّة وقيمها الإنسانيّة، في أعمال جسّدت موهبة واعدة وحسًّا فنيًّا راقيًّا.
+وفي ختام الاحتفال، وُزِّعت الجوائز على المدارس والتلامذة الفائزين بالمراكز الثلاثة الأولى، فجاءت النذتائج على النحو الآتي:
+• الجائزة الأولى: التلميذ ألبير ضاهر من مدرسة بشلّي الرسميّة.
+• الجائزة الثانية: التلميذ جيمس أبي حنّا من مدرسة جبيل المتوسّطة الرسميّة المختلطة.
+• الجائزة الثالثة: التلميذة جانيت خليل من مدرسة ذوق مِصبح الرسميّة المختلطة.
+كما مُنحت جوائز تكريميّة للتلامذة الخمسة عشر الّذين تأهلوا إلى المرحلة النهائيّة من أصل 151 تلميذًا شاركوا في المسابقة من محافظتي بيروت وجبل لبنان، تقديرًا لمواهبهم وتشجيعًا لهم على مواصلة الإبداع.
+واختُتم الاحتفال في أجواء عكست عمق الشراكة الثقافيّة والتربويّة بين لبنان واليابان، وأكّدت أن الفنّ يبقى لغةً إنسانيّةً جامعة، وجسرًا للحوار والتلاقي بين الشعوب، ووسيلةً فاعلةً لترسيخ قيم الانفتاح والإبداع لدى الأجيال الناشئة.</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>2026-10-29T11:14:19.322334+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
